--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rc2c78d829ff94cca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R4e6ac68f2a16468e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R72403a433ea2432c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R5ef16a4297e8417d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R495b8202929c4864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R8f4fb35bc6c14a9e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rbfe00115a2924ce8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="Recaeb1586c734fb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R81fb4a25b97c40a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rdc20f93f0fa6476b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -580,125 +580,125 @@
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>南阳吾悦</x:v>
+        <x:v>襄阳高新万达</x:v>
       </x:c>
       <x:c r="C2" s="17" t="str">
-        <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
+        <x:v>完成率77.70%&lt;100%；新签小卡率66.15%&gt;40%</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
+        <x:v>总营收27207；完成率77.70%；新签小/中/大卡43/20/2；新客、老客、续费率待核</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
+2. 完成率77.70%，距目标还差7809元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
+3. 当前截图已识别新签小卡43张、中卡20张、大卡2张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+      </x:c>
+      <x:c r="G2" s="18" t="str"/>
+    </x:row>
+    <x:row r="3" ht="118" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>南阳吾悦</x:v>
+      </x:c>
+      <x:c r="C3" s="17" t="str">
+        <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str"/>
+      <x:c r="E3" s="11" t="str">
         <x:v>总营收19374；完成率53.96%；新签小/中/大卡22/8/2；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从21993元变为19374元，减少2619元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率53.96%，距目标还差16530元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡22张、中卡8张、大卡2张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str"/>
-    </x:row>
-    <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
+      <x:c r="G3" s="18" t="str"/>
+    </x:row>
+    <x:row r="4" ht="118" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
         <x:v>许昌魏都万达</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>完成率72.05%&lt;100%；新签小卡率57.69%&gt;40%</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str"/>
-      <x:c r="E3" s="11" t="str">
+      <x:c r="D4" s="18" t="str"/>
+      <x:c r="E4" s="11" t="str">
         <x:v>总营收17482；完成率72.05%；新签小/中/大卡15/11/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="str">
+      <x:c r="F4" s="11" t="str">
         <x:v>1. 本周总营收17482元，请列出贡献最大的3笔订单、员工和卡型。
 2. 完成率72.05%，距目标还差6782元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡15张、中卡11张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str"/>
-    </x:row>
-    <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="G4" s="18" t="str"/>
+    </x:row>
+    <x:row r="5" ht="118" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
         <x:v>商丘万达</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="str">
+      <x:c r="C5" s="17" t="str">
         <x:v>完成率82.39%&lt;100%；新签小卡率58.33%&gt;40%</x:v>
       </x:c>
-      <x:c r="D4" s="18" t="str"/>
-      <x:c r="E4" s="11" t="str">
+      <x:c r="D5" s="18" t="str"/>
+      <x:c r="E5" s="11" t="str">
         <x:v>总营收17406；完成率82.39%；新签小/中/大卡14/5/5；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="str">
+      <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从15461元变为17406元，增加1945元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率82.39%，距目标还差3720元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡14张、中卡5张、大卡5张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G4" s="18" t="str"/>
-    </x:row>
-    <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="G5" s="18" t="str"/>
+    </x:row>
+    <x:row r="6" ht="118" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
         <x:v>南阳万达</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
-        <x:v>完成率49.01%&lt;100%；新签小卡率65.22%&gt;40%</x:v>
-      </x:c>
-      <x:c r="D5" s="18" t="str"/>
-      <x:c r="E5" s="11" t="str">
-        <x:v>总营收14716；完成率49.01%；新签小/中/大卡15/5/3；新客、老客、续费率待核</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
+      <x:c r="C6" s="17" t="str">
+        <x:v>完成率49.01%&lt;100%；新签小卡率66.67%&gt;40%</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str"/>
+      <x:c r="E6" s="11" t="str">
+        <x:v>总营收14716；完成率49.01%；新签小/中/大卡18/6/3；新客、老客、续费率待核</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从24886元变为14716元，减少10170元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率49.01%，距目标还差15311元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡15张、中卡5张、大卡3张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
-      </x:c>
-      <x:c r="G5" s="18" t="str"/>
-    </x:row>
-    <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
+3. 当前截图已识别新签小卡18张、中卡6张、大卡3张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="str"/>
+    </x:row>
+    <x:row r="7" ht="118" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
         <x:v>信阳万达</x:v>
       </x:c>
-      <x:c r="C6" s="17" t="str">
+      <x:c r="C7" s="17" t="str">
         <x:v>完成率66.01%&lt;100%；新签小卡率60.71%&gt;40%</x:v>
       </x:c>
-      <x:c r="D6" s="18" t="str"/>
-      <x:c r="E6" s="11" t="str">
+      <x:c r="D7" s="18" t="str"/>
+      <x:c r="E7" s="11" t="str">
         <x:v>总营收11921；完成率66.01%；新签小/中/大卡17/10/1；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="str">
+      <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从10690元变为11921元，增加1231元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率66.01%，距目标还差6139元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡17张、中卡10张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G6" s="18" t="str"/>
-    </x:row>
-    <x:row r="7" ht="118" customHeight="1">
-      <x:c r="A7" s="22" t="str">
-        <x:v>黄灯</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>襄阳高新万达</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:v>完成率77.70%&lt;100%；新签小卡率53.13%&gt;40%</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str"/>
-      <x:c r="E7" s="11" t="str">
-        <x:v>总营收27207；完成率77.70%；新签小/中/大卡34/28/2；新客、老客、续费率待核</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
-        <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
-2. 完成率77.70%，距目标还差7809元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡34张、中卡28张、大卡2张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
-      </x:c>
       <x:c r="G7" s="18" t="str"/>
     </x:row>
     <x:row r="8" ht="118" customHeight="1">
@@ -706,104 +706,104 @@
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>洛阳中州万达</x:v>
+        <x:v>洛阳泉舜</x:v>
       </x:c>
       <x:c r="C8" s="17" t="str">
-        <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
+        <x:v>完成率77.40%&lt;100%；新签小卡率56.41%&gt;40%</x:v>
       </x:c>
       <x:c r="D8" s="18" t="str"/>
       <x:c r="E8" s="11" t="str">
+        <x:v>总营收34016；完成率77.40%；新签小/中/大卡22/11/6；新客、老客、续费率待核</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
+2. 完成率77.40%，距目标还差9934元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
+3. 当前截图已识别新签小卡22张、中卡11张、大卡6张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+      </x:c>
+      <x:c r="G8" s="18" t="str"/>
+    </x:row>
+    <x:row r="9" ht="118" customHeight="1">
+      <x:c r="A9" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>洛阳中州万达</x:v>
+      </x:c>
+      <x:c r="C9" s="17" t="str">
+        <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="str"/>
+      <x:c r="E9" s="11" t="str">
         <x:v>总营收18990；完成率76.64%；新签小/中/大卡35/12/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F8" s="11" t="str">
+      <x:c r="F9" s="11" t="str">
         <x:v>1. 总营收从15679元变为18990元，增加3311元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率76.64%，距目标还差5788元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡35张、中卡12张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G8" s="18" t="str"/>
-    </x:row>
-    <x:row r="9" ht="118" customHeight="1">
-      <x:c r="A9" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
+      <x:c r="G9" s="18" t="str"/>
+    </x:row>
+    <x:row r="10" ht="118" customHeight="1">
+      <x:c r="A10" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
         <x:v>郑州惠济万达</x:v>
       </x:c>
-      <x:c r="C9" s="17" t="str">
+      <x:c r="C10" s="17" t="str">
         <x:v>完成率56.45%&lt;100%</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="str"/>
-      <x:c r="E9" s="11" t="str">
+      <x:c r="D10" s="18" t="str"/>
+      <x:c r="E10" s="11" t="str">
         <x:v>总营收12223；完成率56.45%；新签小/中/大卡4/11/1；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F9" s="11" t="str">
+      <x:c r="F10" s="11" t="str">
         <x:v>1. 总营收从17422元变为12223元，减少5199元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率56.45%，距目标还差9431元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡4张、中卡11张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G9" s="18" t="str"/>
-    </x:row>
-    <x:row r="10" ht="118" customHeight="1">
-      <x:c r="A10" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
+      <x:c r="G10" s="18" t="str"/>
+    </x:row>
+    <x:row r="11" ht="118" customHeight="1">
+      <x:c r="A11" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
         <x:v>新乡万达</x:v>
       </x:c>
-      <x:c r="C10" s="17" t="str">
+      <x:c r="C11" s="17" t="str">
         <x:v>完成率61.88%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
-      <x:c r="D10" s="18" t="str"/>
-      <x:c r="E10" s="11" t="str">
+      <x:c r="D11" s="18" t="str"/>
+      <x:c r="E11" s="11" t="str">
         <x:v>总营收11731；完成率61.88%；新签小/中/大卡3/4/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F10" s="11" t="str">
+      <x:c r="F11" s="11" t="str">
         <x:v>1. 总营收从14444元变为11731元，减少2713元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率61.88%，距目标还差7228元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡3张、中卡4张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G10" s="18" t="str"/>
-    </x:row>
-    <x:row r="11" ht="118" customHeight="1">
-      <x:c r="A11" s="22" t="str">
+      <x:c r="G11" s="18" t="str"/>
+    </x:row>
+    <x:row r="12" ht="118" customHeight="1">
+      <x:c r="A12" s="22" t="str">
         <x:v>黄灯</x:v>
       </x:c>
-      <x:c r="B11" s="11" t="str">
+      <x:c r="B12" s="11" t="str">
         <x:v>焦作万达</x:v>
       </x:c>
-      <x:c r="C11" s="17" t="str">
+      <x:c r="C12" s="17" t="str">
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
-      <x:c r="D11" s="18" t="str"/>
-      <x:c r="E11" s="11" t="str">
+      <x:c r="D12" s="18" t="str"/>
+      <x:c r="E12" s="11" t="str">
         <x:v>总营收36882；完成率91.25%；新签小/中/大卡23/19/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F11" s="11" t="str">
+      <x:c r="F12" s="11" t="str">
         <x:v>1. 总营收从32869元变为36882元，增加4014元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率91.25%，距目标还差3537元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡23张、中卡19张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G11" s="18" t="str"/>
-    </x:row>
-    <x:row r="12" ht="118" customHeight="1">
-      <x:c r="A12" s="22" t="str">
-        <x:v>黄灯</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>洛阳泉舜</x:v>
-      </x:c>
-      <x:c r="C12" s="17" t="str">
-        <x:v>完成率77.40%&lt;100%；新签小卡率53.49%&gt;40%</x:v>
-      </x:c>
-      <x:c r="D12" s="18" t="str"/>
-      <x:c r="E12" s="11" t="str">
-        <x:v>总营收34016；完成率77.40%；新签小/中/大卡23/14/6；新客、老客、续费率待核</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="str">
-        <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
-2. 完成率77.40%，距目标还差9934元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡23张、中卡14张、大卡6张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
-      </x:c>
       <x:c r="G12" s="18" t="str"/>
     </x:row>
     <x:row r="13" ht="118" customHeight="1">
@@ -818,12 +818,12 @@
       </x:c>
       <x:c r="D13" s="18" t="str"/>
       <x:c r="E13" s="11" t="str">
-        <x:v>总营收16093；完成率84.85%；新签小/中/大卡1/9/12；新客、老客、续费率待核</x:v>
+        <x:v>总营收16093；完成率84.85%；新签小/中/大卡1/10/16；新客、老客、续费率待核</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
         <x:v>1. 总营收从13881元变为16093元，增加2212元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率84.85%，距目标还差2873元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡1张、中卡9张、大卡12张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡1张、中卡10张、大卡16张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G13" s="18" t="str"/>
     </x:row>
@@ -839,12 +839,12 @@
       </x:c>
       <x:c r="D14" s="18" t="str"/>
       <x:c r="E14" s="11" t="str">
-        <x:v>总营收27184；完成率133.32%；新签小/中/大卡9/21/4；新客、老客、续费率待核</x:v>
+        <x:v>总营收27184；完成率133.32%；新签小/中/大卡9/21/5；新客、老客、续费率待核</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
         <x:v>1. 总营收从14630元变为27184元，增加12553元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率133.32%，距目标还差0元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡9张、中卡21张、大卡4张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡9张、中卡21张、大卡5张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G14" s="18" t="str"/>
     </x:row>
@@ -977,7 +977,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reafdab75c8d04657"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R967cddafbe644f1a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1023,131 +1023,131 @@
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>南阳吾悦</x:v>
+        <x:v>襄阳高新万达</x:v>
       </x:c>
       <x:c r="C2" s="17" t="str">
-        <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
+        <x:v>完成率77.70%&lt;100%；新签小卡率66.15%&gt;40%</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
+        <x:v>总营收27207；完成率77.70%；新签小/中/大卡43/20/2；新客、老客、续费率待核</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
+2. 完成率77.70%，距目标还差7809元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
+3. 当前截图已识别新签小卡43张、中卡20张、大卡2张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+      </x:c>
+      <x:c r="G2" s="18" t="str"/>
+    </x:row>
+    <x:row r="3" ht="118" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>南阳吾悦</x:v>
+      </x:c>
+      <x:c r="C3" s="17" t="str">
+        <x:v>完成率53.96%&lt;100%；新签小卡率68.75%&gt;40%</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str"/>
+      <x:c r="E3" s="11" t="str">
         <x:v>总营收19374；完成率53.96%；新签小/中/大卡22/8/2；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从21993元变为19374元，减少2619元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率53.96%，距目标还差16530元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡22张、中卡8张、大卡2张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str"/>
-    </x:row>
-    <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
+      <x:c r="G3" s="18" t="str"/>
+    </x:row>
+    <x:row r="4" ht="118" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
         <x:v>许昌魏都万达</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>完成率72.05%&lt;100%；新签小卡率57.69%&gt;40%</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str"/>
-      <x:c r="E3" s="11" t="str">
+      <x:c r="D4" s="18" t="str"/>
+      <x:c r="E4" s="11" t="str">
         <x:v>总营收17482；完成率72.05%；新签小/中/大卡15/11/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="str">
+      <x:c r="F4" s="11" t="str">
         <x:v>1. 本周总营收17482元，请列出贡献最大的3笔订单、员工和卡型。
 2. 完成率72.05%，距目标还差6782元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡15张、中卡11张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str"/>
-    </x:row>
-    <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="G4" s="18" t="str"/>
+    </x:row>
+    <x:row r="5" ht="118" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
         <x:v>商丘万达</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="str">
+      <x:c r="C5" s="17" t="str">
         <x:v>完成率82.39%&lt;100%；新签小卡率58.33%&gt;40%</x:v>
       </x:c>
-      <x:c r="D4" s="18" t="str"/>
-      <x:c r="E4" s="11" t="str">
+      <x:c r="D5" s="18" t="str"/>
+      <x:c r="E5" s="11" t="str">
         <x:v>总营收17406；完成率82.39%；新签小/中/大卡14/5/5；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="str">
+      <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从15461元变为17406元，增加1945元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率82.39%，距目标还差3720元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡14张、中卡5张、大卡5张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G4" s="18" t="str"/>
-    </x:row>
-    <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="G5" s="18" t="str"/>
+    </x:row>
+    <x:row r="6" ht="118" customHeight="1">
+      <x:c r="A6" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
         <x:v>南阳万达</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
-        <x:v>完成率49.01%&lt;100%；新签小卡率65.22%&gt;40%</x:v>
-      </x:c>
-      <x:c r="D5" s="18" t="str"/>
-      <x:c r="E5" s="11" t="str">
-        <x:v>总营收14716；完成率49.01%；新签小/中/大卡15/5/3；新客、老客、续费率待核</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
+      <x:c r="C6" s="17" t="str">
+        <x:v>完成率49.01%&lt;100%；新签小卡率66.67%&gt;40%</x:v>
+      </x:c>
+      <x:c r="D6" s="18" t="str"/>
+      <x:c r="E6" s="11" t="str">
+        <x:v>总营收14716；完成率49.01%；新签小/中/大卡18/6/3；新客、老客、续费率待核</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从24886元变为14716元，减少10170元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率49.01%，距目标还差15311元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡15张、中卡5张、大卡3张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
-      </x:c>
-      <x:c r="G5" s="18" t="str"/>
-    </x:row>
-    <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
+3. 当前截图已识别新签小卡18张、中卡6张、大卡3张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+      </x:c>
+      <x:c r="G6" s="18" t="str"/>
+    </x:row>
+    <x:row r="7" ht="118" customHeight="1">
+      <x:c r="A7" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
         <x:v>信阳万达</x:v>
       </x:c>
-      <x:c r="C6" s="17" t="str">
+      <x:c r="C7" s="17" t="str">
         <x:v>完成率66.01%&lt;100%；新签小卡率60.71%&gt;40%</x:v>
       </x:c>
-      <x:c r="D6" s="18" t="str"/>
-      <x:c r="E6" s="11" t="str">
+      <x:c r="D7" s="18" t="str"/>
+      <x:c r="E7" s="11" t="str">
         <x:v>总营收11921；完成率66.01%；新签小/中/大卡17/10/1；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F6" s="11" t="str">
+      <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从10690元变为11921元，增加1231元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率66.01%，距目标还差6139元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡17张、中卡10张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G6" s="18" t="str"/>
-    </x:row>
-    <x:row r="7" ht="118" customHeight="1">
-      <x:c r="A7" s="22" t="str">
-        <x:v>黄灯</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>襄阳高新万达</x:v>
-      </x:c>
-      <x:c r="C7" s="17" t="str">
-        <x:v>完成率77.70%&lt;100%；新签小卡率53.13%&gt;40%</x:v>
-      </x:c>
-      <x:c r="D7" s="18" t="str"/>
-      <x:c r="E7" s="11" t="str">
-        <x:v>总营收27207；完成率77.70%；新签小/中/大卡34/28/2；新客、老客、续费率待核</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
-        <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
-2. 完成率77.70%，距目标还差7809元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡34张、中卡28张、大卡2张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
-      </x:c>
       <x:c r="G7" s="18" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98433bbf5c6f41f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1f8cffc788940cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1193,104 +1193,104 @@
         <x:v>红灯</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>洛阳中州万达</x:v>
+        <x:v>洛阳泉舜</x:v>
       </x:c>
       <x:c r="C2" s="17" t="str">
-        <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
+        <x:v>完成率77.40%&lt;100%；新签小卡率56.41%&gt;40%</x:v>
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
+        <x:v>总营收34016；完成率77.40%；新签小/中/大卡22/11/6；新客、老客、续费率待核</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
+2. 完成率77.40%，距目标还差9934元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
+3. 当前截图已识别新签小卡22张、中卡11张、大卡6张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+      </x:c>
+      <x:c r="G2" s="18" t="str"/>
+    </x:row>
+    <x:row r="3" ht="118" customHeight="1">
+      <x:c r="A3" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>洛阳中州万达</x:v>
+      </x:c>
+      <x:c r="C3" s="17" t="str">
+        <x:v>完成率76.64%&lt;100%；新签小卡率74.47%&gt;40%</x:v>
+      </x:c>
+      <x:c r="D3" s="18" t="str"/>
+      <x:c r="E3" s="11" t="str">
         <x:v>总营收18990；完成率76.64%；新签小/中/大卡35/12/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F2" s="11" t="str">
+      <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从15679元变为18990元，增加3311元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率76.64%，距目标还差5788元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡35张、中卡12张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G2" s="18" t="str"/>
-    </x:row>
-    <x:row r="3" ht="118" customHeight="1">
-      <x:c r="A3" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
+      <x:c r="G3" s="18" t="str"/>
+    </x:row>
+    <x:row r="4" ht="118" customHeight="1">
+      <x:c r="A4" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
         <x:v>郑州惠济万达</x:v>
       </x:c>
-      <x:c r="C3" s="17" t="str">
+      <x:c r="C4" s="17" t="str">
         <x:v>完成率56.45%&lt;100%</x:v>
       </x:c>
-      <x:c r="D3" s="18" t="str"/>
-      <x:c r="E3" s="11" t="str">
+      <x:c r="D4" s="18" t="str"/>
+      <x:c r="E4" s="11" t="str">
         <x:v>总营收12223；完成率56.45%；新签小/中/大卡4/11/1；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F3" s="11" t="str">
+      <x:c r="F4" s="11" t="str">
         <x:v>1. 总营收从17422元变为12223元，减少5199元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率56.45%，距目标还差9431元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡4张、中卡11张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G3" s="18" t="str"/>
-    </x:row>
-    <x:row r="4" ht="118" customHeight="1">
-      <x:c r="A4" s="16" t="str">
-        <x:v>红灯</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
+      <x:c r="G4" s="18" t="str"/>
+    </x:row>
+    <x:row r="5" ht="118" customHeight="1">
+      <x:c r="A5" s="16" t="str">
+        <x:v>红灯</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
         <x:v>新乡万达</x:v>
       </x:c>
-      <x:c r="C4" s="17" t="str">
+      <x:c r="C5" s="17" t="str">
         <x:v>完成率61.88%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
       </x:c>
-      <x:c r="D4" s="18" t="str"/>
-      <x:c r="E4" s="11" t="str">
+      <x:c r="D5" s="18" t="str"/>
+      <x:c r="E5" s="11" t="str">
         <x:v>总营收11731；完成率61.88%；新签小/中/大卡3/4/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F4" s="11" t="str">
+      <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从14444元变为11731元，减少2713元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率61.88%，距目标还差7228元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡3张、中卡4张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G4" s="18" t="str"/>
-    </x:row>
-    <x:row r="5" ht="118" customHeight="1">
-      <x:c r="A5" s="22" t="str">
+      <x:c r="G5" s="18" t="str"/>
+    </x:row>
+    <x:row r="6" ht="118" customHeight="1">
+      <x:c r="A6" s="22" t="str">
         <x:v>黄灯</x:v>
       </x:c>
-      <x:c r="B5" s="11" t="str">
+      <x:c r="B6" s="11" t="str">
         <x:v>焦作万达</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="str">
+      <x:c r="C6" s="17" t="str">
         <x:v>完成率91.25%&lt;100%；新签小卡率54.76%&gt;40%</x:v>
       </x:c>
-      <x:c r="D5" s="18" t="str"/>
-      <x:c r="E5" s="11" t="str">
+      <x:c r="D6" s="18" t="str"/>
+      <x:c r="E6" s="11" t="str">
         <x:v>总营收36882；完成率91.25%；新签小/中/大卡23/19/0；新客、老客、续费率待核</x:v>
       </x:c>
-      <x:c r="F5" s="11" t="str">
+      <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从32869元变为36882元，增加4014元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率91.25%，距目标还差3537元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡23张、中卡19张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
-      <x:c r="G5" s="18" t="str"/>
-    </x:row>
-    <x:row r="6" ht="118" customHeight="1">
-      <x:c r="A6" s="22" t="str">
-        <x:v>黄灯</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>洛阳泉舜</x:v>
-      </x:c>
-      <x:c r="C6" s="17" t="str">
-        <x:v>完成率77.40%&lt;100%；新签小卡率53.49%&gt;40%</x:v>
-      </x:c>
-      <x:c r="D6" s="18" t="str"/>
-      <x:c r="E6" s="11" t="str">
-        <x:v>总营收34016；完成率77.40%；新签小/中/大卡23/14/6；新客、老客、续费率待核</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="str">
-        <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
-2. 完成率77.40%，距目标还差9934元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡23张、中卡14张、大卡6张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
-      </x:c>
       <x:c r="G6" s="18" t="str"/>
     </x:row>
     <x:row r="7" ht="118" customHeight="1">
@@ -1305,12 +1305,12 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收16093；完成率84.85%；新签小/中/大卡1/9/12；新客、老客、续费率待核</x:v>
+        <x:v>总营收16093；完成率84.85%；新签小/中/大卡1/10/16；新客、老客、续费率待核</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从13881元变为16093元，增加2212元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率84.85%，距目标还差2873元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡1张、中卡9张、大卡12张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡1张、中卡10张、大卡16张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str"/>
     </x:row>
@@ -1326,19 +1326,19 @@
       </x:c>
       <x:c r="D8" s="18" t="str"/>
       <x:c r="E8" s="11" t="str">
-        <x:v>总营收27184；完成率133.32%；新签小/中/大卡9/21/4；新客、老客、续费率待核</x:v>
+        <x:v>总营收27184；完成率133.32%；新签小/中/大卡9/21/5；新客、老客、续费率待核</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
         <x:v>1. 总营收从14630元变为27184元，增加12553元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率133.32%，距目标还差0元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡9张、中卡21张、大卡4张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡9张、中卡21张、大卡5张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G8" s="18" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f0ae8b533704841"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe98c04eed94a36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1508,7 +1508,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9af509bcc594590"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d69b70434bd454e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R8f4fb35bc6c14a9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rbfe00115a2924ce8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="Recaeb1586c734fb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R81fb4a25b97c40a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rdc20f93f0fa6476b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rd9a81b5cbf084fb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rce8c6462d6504c1c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="Rd733a23648e347fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R4280dae628414a51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R396677cae2104c8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -507,7 +507,7 @@
         <x:v>续费率</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>用户截图中的续费率原值；门店级本周原值未在可核截图中逐店确认，统一标记待核，不自行反算。</x:v>
+        <x:v>门店续费率使用最新小程序截图原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -515,22 +515,30 @@
         <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数/识别到的新签卡数；本周门店卡型截图OCR合计617张，品牌截图为630张新签卡，差额13张待人工核对。</x:v>
+        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>排名</x:v>
+        <x:v>总办卡率</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>店员卡型页保留截图排名；金额排名本周截图横向字段不完整，未用旧周数据冒充本周金额。</x:v>
+        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B8" s="4" t="str">
+        <x:v>店员卡型页保留截图排名；金额排名本周截图横向字段不完整，未用旧周数据冒充本周金额。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="4" t="str">
         <x:v>更新方式</x:v>
       </x:c>
-      <x:c r="B8" s="4" t="str">
+      <x:c r="B9" s="4" t="str">
         <x:v>HTML、周报核对底表、城市经理问题闭环填写表使用同一周期和同一门店口径。</x:v>
       </x:c>
     </x:row>
@@ -587,7 +595,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收27207；完成率77.70%；新签小/中/大卡43/20/2；新客、老客、续费率待核</x:v>
+        <x:v>总营收27207；完成率77.70%；新签营收21837；新签小/中/大卡43/20/2；续费率6.48%；续卡金额2768；扫楼金额3923</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -608,7 +616,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收19374；完成率53.96%；新签小/中/大卡22/8/2；新客、老客、续费率待核</x:v>
+        <x:v>总营收19374；完成率53.96%；新签营收11529；新签小/中/大卡22/8/2；续费率7.95%；续卡金额5949；扫楼金额2031</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从21993元变为19374元，减少2619元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -629,7 +637,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收17482；完成率72.05%；新签小/中/大卡15/11/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收17482；完成率72.05%；新签营收9243；新签小/中/大卡15/11/0；续费率10%；续卡金额6280；扫楼金额3198</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 本周总营收17482元，请列出贡献最大的3笔订单、员工和卡型。
@@ -650,7 +658,7 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收17406；完成率82.39%；新签小/中/大卡14/5/5；新客、老客、续费率待核</x:v>
+        <x:v>总营收17406；完成率82.39%；新签营收7748；新签小/中/大卡14/5/5；续费率13.87%；续卡金额7964；扫楼金额2987</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从15461元变为17406元，增加1945元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -671,7 +679,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收14716；完成率49.01%；新签小/中/大卡18/6/3；新客、老客、续费率待核</x:v>
+        <x:v>总营收14716；完成率49.01%；新签营收9833；新签小/中/大卡18/6/3；续费率4.27%；续卡金额3399；扫楼金额491</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从24886元变为14716元，减少10170元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -688,16 +696,16 @@
         <x:v>信阳万达</x:v>
       </x:c>
       <x:c r="C7" s="17" t="str">
-        <x:v>完成率66.01%&lt;100%；新签小卡率60.71%&gt;40%</x:v>
+        <x:v>完成率66.01%&lt;100%</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收11921；完成率66.01%；新签小/中/大卡17/10/1；新客、老客、续费率待核</x:v>
+        <x:v>总营收11921；完成率66.01%；新签营收9035；新签小/中/大卡8/18/1；续费率8%；续卡金额1486.15；扫楼金额3279.4</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从10690元变为11921元，增加1231元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率66.01%，距目标还差6139元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡17张、中卡10张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡8张、中卡18张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str"/>
     </x:row>
@@ -713,7 +721,7 @@
       </x:c>
       <x:c r="D8" s="18" t="str"/>
       <x:c r="E8" s="11" t="str">
-        <x:v>总营收34016；完成率77.40%；新签小/中/大卡22/11/6；新客、老客、续费率待核</x:v>
+        <x:v>总营收34016；完成率77.40%；新签营收16461；新签小/中/大卡22/11/6；续费率12.56%；续卡金额12299；扫楼金额8325</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
         <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -734,7 +742,7 @@
       </x:c>
       <x:c r="D9" s="18" t="str"/>
       <x:c r="E9" s="11" t="str">
-        <x:v>总营收18990；完成率76.64%；新签小/中/大卡35/12/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收18990；完成率76.64%；新签营收14184；新签小/中/大卡35/12/0；续费率4.3%；续卡金额1600；扫楼金额3349</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
         <x:v>1. 总营收从15679元变为18990元，增加3311元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -755,12 +763,12 @@
       </x:c>
       <x:c r="D10" s="18" t="str"/>
       <x:c r="E10" s="11" t="str">
-        <x:v>总营收12223；完成率56.45%；新签小/中/大卡4/11/1；新客、老客、续费率待核</x:v>
+        <x:v>总营收12223；完成率56.45%；新签营收8912；新签小/中/大卡4/13/1；续费率7.87%；续卡金额3200；扫楼金额2782</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
         <x:v>1. 总营收从17422元变为12223元，减少5199元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率56.45%，距目标还差9431元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡4张、中卡11张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡4张、中卡13张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G10" s="18" t="str"/>
     </x:row>
@@ -772,16 +780,16 @@
         <x:v>新乡万达</x:v>
       </x:c>
       <x:c r="C11" s="17" t="str">
-        <x:v>完成率61.88%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
+        <x:v>完成率61.88%&lt;100%</x:v>
       </x:c>
       <x:c r="D11" s="18" t="str"/>
       <x:c r="E11" s="11" t="str">
-        <x:v>总营收11731；完成率61.88%；新签小/中/大卡3/4/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收11731；完成率61.88%；新签营收4837；新签小/中/大卡4/8/0；续费率5.26%；续卡金额2800；扫楼金额2243.2</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
         <x:v>1. 总营收从14444元变为11731元，减少2713元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率61.88%，距目标还差7228元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡3张、中卡4张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡4张、中卡8张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G11" s="18" t="str"/>
     </x:row>
@@ -797,7 +805,7 @@
       </x:c>
       <x:c r="D12" s="18" t="str"/>
       <x:c r="E12" s="11" t="str">
-        <x:v>总营收36882；完成率91.25%；新签小/中/大卡23/19/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收36882；完成率91.25%；新签营收15240；新签小/中/大卡23/19/0；续费率7.34%；续卡金额17800；扫楼金额8531.2</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
         <x:v>1. 总营收从32869元变为36882元，增加4014元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -818,7 +826,7 @@
       </x:c>
       <x:c r="D13" s="18" t="str"/>
       <x:c r="E13" s="11" t="str">
-        <x:v>总营收16093；完成率84.85%；新签小/中/大卡1/10/16；新客、老客、续费率待核</x:v>
+        <x:v>总营收16093；完成率84.85%；新签营收11008；新签小/中/大卡1/10/16；续费率13.75%；续卡金额4089；扫楼金额3069</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
         <x:v>1. 总营收从13881元变为16093元，增加2212元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -839,7 +847,7 @@
       </x:c>
       <x:c r="D14" s="18" t="str"/>
       <x:c r="E14" s="11" t="str">
-        <x:v>总营收27184；完成率133.32%；新签小/中/大卡9/21/5；新客、老客、续费率待核</x:v>
+        <x:v>总营收27184；完成率133.32%；新签营收22423；新签小/中/大卡9/21/5；续费率5.1%；续卡金额1800；扫楼金额1814</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
         <x:v>1. 总营收从14630元变为27184元，增加12553元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -860,7 +868,7 @@
       </x:c>
       <x:c r="D15" s="18" t="str"/>
       <x:c r="E15" s="11" t="str">
-        <x:v>总营收30549；完成率89.02%；新签小/中/大卡32/17/2；新客、老客、续费率待核</x:v>
+        <x:v>总营收30549；完成率89.02%；新签营收20415；新签小/中/大卡32/17/2；续费率11.11%；续卡金额6900；扫楼金额9649</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
         <x:v>1. 总营收从24097元变为30549元，增加6452元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -881,7 +889,7 @@
       </x:c>
       <x:c r="D16" s="18" t="str"/>
       <x:c r="E16" s="11" t="str">
-        <x:v>总营收30206；完成率68.71%；新签小/中/大卡37/14/6；新客、老客、续费率待核</x:v>
+        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额1500；扫楼金额7715</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
         <x:v>1. 总营收从33802元变为30206元，减少3596元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -902,7 +910,7 @@
       </x:c>
       <x:c r="D17" s="18" t="str"/>
       <x:c r="E17" s="11" t="str">
-        <x:v>总营收21882；完成率70.36%；新签小/中/大卡16/9/3；新客、老客、续费率待核</x:v>
+        <x:v>总营收21882；完成率70.36%；新签营收11554；新签小/中/大卡16/9/3；续费率8.93%；续卡金额7400；扫楼金额2287</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
         <x:v>1. 总营收从20896元变为21882元，增加986元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -923,12 +931,12 @@
       </x:c>
       <x:c r="D18" s="18" t="str"/>
       <x:c r="E18" s="11" t="str">
-        <x:v>总营收8696；完成率52.35%；新签小/中/大卡3/6/9；新客、老客、续费率待核</x:v>
+        <x:v>总营收8696；完成率52.35%；新签营收5862；新签小/中/大卡3/6/8；续费率7.32%；续卡金额957；扫楼金额1771</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
         <x:v>1. 本周总营收8696元，请列出贡献最大的3笔订单、员工和卡型。
 2. 完成率52.35%，距目标还差7914元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡3张、中卡6张、大卡9张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡3张、中卡6张、大卡8张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G18" s="18" t="str"/>
     </x:row>
@@ -944,7 +952,7 @@
       </x:c>
       <x:c r="D19" s="18" t="str"/>
       <x:c r="E19" s="11" t="str">
-        <x:v>总营收7175；完成率40.63%；新签小/中/大卡4/9/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收7175；完成率40.63%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
         <x:v>1. 总营收从8389元变为7175元，减少1214元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -965,7 +973,7 @@
       </x:c>
       <x:c r="D20" s="18" t="str"/>
       <x:c r="E20" s="11" t="str">
-        <x:v>总营收25527；完成率78.67%；新签小/中/大卡18/20/4；新客、老客、续费率待核</x:v>
+        <x:v>总营收25527；完成率78.67%；新签营收17570；新签小/中/大卡18/20/4；续费率7.83%；续卡金额3920；扫楼金额1000</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
         <x:v>1. 总营收从29658元变为25527元，减少4131元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -977,7 +985,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R967cddafbe644f1a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4a4fd26c8f845dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1030,7 +1038,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收27207；完成率77.70%；新签小/中/大卡43/20/2；新客、老客、续费率待核</x:v>
+        <x:v>总营收27207；完成率77.70%；新签营收21837；新签小/中/大卡43/20/2；续费率6.48%；续卡金额2768；扫楼金额3923</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1051,7 +1059,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收19374；完成率53.96%；新签小/中/大卡22/8/2；新客、老客、续费率待核</x:v>
+        <x:v>总营收19374；完成率53.96%；新签营收11529；新签小/中/大卡22/8/2；续费率7.95%；续卡金额5949；扫楼金额2031</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从21993元变为19374元，减少2619元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1072,7 +1080,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收17482；完成率72.05%；新签小/中/大卡15/11/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收17482；完成率72.05%；新签营收9243；新签小/中/大卡15/11/0；续费率10%；续卡金额6280；扫楼金额3198</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 本周总营收17482元，请列出贡献最大的3笔订单、员工和卡型。
@@ -1093,7 +1101,7 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收17406；完成率82.39%；新签小/中/大卡14/5/5；新客、老客、续费率待核</x:v>
+        <x:v>总营收17406；完成率82.39%；新签营收7748；新签小/中/大卡14/5/5；续费率13.87%；续卡金额7964；扫楼金额2987</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从15461元变为17406元，增加1945元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1114,7 +1122,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收14716；完成率49.01%；新签小/中/大卡18/6/3；新客、老客、续费率待核</x:v>
+        <x:v>总营收14716；完成率49.01%；新签营收9833；新签小/中/大卡18/6/3；续费率4.27%；续卡金额3399；扫楼金额491</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从24886元变为14716元，减少10170元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1131,23 +1139,23 @@
         <x:v>信阳万达</x:v>
       </x:c>
       <x:c r="C7" s="17" t="str">
-        <x:v>完成率66.01%&lt;100%；新签小卡率60.71%&gt;40%</x:v>
+        <x:v>完成率66.01%&lt;100%</x:v>
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收11921；完成率66.01%；新签小/中/大卡17/10/1；新客、老客、续费率待核</x:v>
+        <x:v>总营收11921；完成率66.01%；新签营收9035；新签小/中/大卡8/18/1；续费率8%；续卡金额1486.15；扫楼金额3279.4</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从10690元变为11921元，增加1231元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率66.01%，距目标还差6139元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡17张、中卡10张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡8张、中卡18张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G7" s="18" t="str"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1f8cffc788940cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcda9e7b08e7a450f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1200,7 +1208,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收34016；完成率77.40%；新签小/中/大卡22/11/6；新客、老客、续费率待核</x:v>
+        <x:v>总营收34016；完成率77.40%；新签营收16461；新签小/中/大卡22/11/6；续费率12.56%；续卡金额12299；扫楼金额8325</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1221,7 +1229,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收18990；完成率76.64%；新签小/中/大卡35/12/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收18990；完成率76.64%；新签营收14184；新签小/中/大卡35/12/0；续费率4.3%；续卡金额1600；扫楼金额3349</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从15679元变为18990元，增加3311元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1242,12 +1250,12 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收12223；完成率56.45%；新签小/中/大卡4/11/1；新客、老客、续费率待核</x:v>
+        <x:v>总营收12223；完成率56.45%；新签营收8912；新签小/中/大卡4/13/1；续费率7.87%；续卡金额3200；扫楼金额2782</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 总营收从17422元变为12223元，减少5199元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率56.45%，距目标还差9431元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡4张、中卡11张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡4张、中卡13张、大卡1张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G4" s="18" t="str"/>
     </x:row>
@@ -1259,16 +1267,16 @@
         <x:v>新乡万达</x:v>
       </x:c>
       <x:c r="C5" s="17" t="str">
-        <x:v>完成率61.88%&lt;100%；新签小卡率42.86%&gt;40%</x:v>
+        <x:v>完成率61.88%&lt;100%</x:v>
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收11731；完成率61.88%；新签小/中/大卡3/4/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收11731；完成率61.88%；新签营收4837；新签小/中/大卡4/8/0；续费率5.26%；续卡金额2800；扫楼金额2243.2</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从14444元变为11731元，减少2713元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
 2. 完成率61.88%，距目标还差7228元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡3张、中卡4张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡4张、中卡8张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G5" s="18" t="str"/>
     </x:row>
@@ -1284,7 +1292,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收36882；完成率91.25%；新签小/中/大卡23/19/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收36882；完成率91.25%；新签营收15240；新签小/中/大卡23/19/0；续费率7.34%；续卡金额17800；扫楼金额8531.2</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从32869元变为36882元，增加4014元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1305,7 +1313,7 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收16093；完成率84.85%；新签小/中/大卡1/10/16；新客、老客、续费率待核</x:v>
+        <x:v>总营收16093；完成率84.85%；新签营收11008；新签小/中/大卡1/10/16；续费率13.75%；续卡金额4089；扫楼金额3069</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从13881元变为16093元，增加2212元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1326,7 +1334,7 @@
       </x:c>
       <x:c r="D8" s="18" t="str"/>
       <x:c r="E8" s="11" t="str">
-        <x:v>总营收27184；完成率133.32%；新签小/中/大卡9/21/5；新客、老客、续费率待核</x:v>
+        <x:v>总营收27184；完成率133.32%；新签营收22423；新签小/中/大卡9/21/5；续费率5.1%；续卡金额1800；扫楼金额1814</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
         <x:v>1. 总营收从14630元变为27184元，增加12553元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1338,7 +1346,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6fe98c04eed94a36"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R313c4d4c9e5f4943"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1391,7 +1399,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收30549；完成率89.02%；新签小/中/大卡32/17/2；新客、老客、续费率待核</x:v>
+        <x:v>总营收30549；完成率89.02%；新签营收20415；新签小/中/大卡32/17/2；续费率11.11%；续卡金额6900；扫楼金额9649</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从24097元变为30549元，增加6452元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1412,7 +1420,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收30206；完成率68.71%；新签小/中/大卡37/14/6；新客、老客、续费率待核</x:v>
+        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额1500；扫楼金额7715</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从33802元变为30206元，减少3596元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1433,7 +1441,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收21882；完成率70.36%；新签小/中/大卡16/9/3；新客、老客、续费率待核</x:v>
+        <x:v>总营收21882；完成率70.36%；新签营收11554；新签小/中/大卡16/9/3；续费率8.93%；续卡金额7400；扫楼金额2287</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 总营收从20896元变为21882元，增加986元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1454,12 +1462,12 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收8696；完成率52.35%；新签小/中/大卡3/6/9；新客、老客、续费率待核</x:v>
+        <x:v>总营收8696；完成率52.35%；新签营收5862；新签小/中/大卡3/6/8；续费率7.32%；续卡金额957；扫楼金额1771</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 本周总营收8696元，请列出贡献最大的3笔订单、员工和卡型。
 2. 完成率52.35%，距目标还差7914元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
-3. 当前截图已识别新签小卡3张、中卡6张、大卡9张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
+3. 当前截图已识别新签小卡3张、中卡6张、大卡8张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G5" s="18" t="str"/>
     </x:row>
@@ -1475,7 +1483,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收7175；完成率40.63%；新签小/中/大卡4/9/0；新客、老客、续费率待核</x:v>
+        <x:v>总营收7175；完成率40.63%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从8389元变为7175元，减少1214元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1496,7 +1504,7 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收25527；完成率78.67%；新签小/中/大卡18/20/4；新客、老客、续费率待核</x:v>
+        <x:v>总营收25527；完成率78.67%；新签营收17570；新签小/中/大卡18/20/4；续费率7.83%；续卡金额3920；扫楼金额1000</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从29658元变为25527元，减少4131元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1508,7 +1516,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d69b70434bd454e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda614b0817134fd0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rd9a81b5cbf084fb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rce8c6462d6504c1c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="Rd733a23648e347fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R4280dae628414a51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R396677cae2104c8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R36504bba54f045d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R86bf612cd5524223"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R64e1eb017a224a17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R6df2bdcbf32543b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R4b67c7f4166b4db0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable4" displayName="WeeklyTable4" ref="A1:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable5" displayName="WeeklyTable5" ref="A1:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G20"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable5" displayName="WeeklyTable5" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable6" displayName="WeeklyTable6" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G7"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WeeklyTable6" displayName="WeeklyTable6" ref="A1:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WeeklyTable7" displayName="WeeklyTable7" ref="A1:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G8"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -256,7 +256,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable7" displayName="WeeklyTable7" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable8" displayName="WeeklyTable8" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G7"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -499,7 +499,7 @@
         <x:v>新客数/老客数</x:v>
       </x:c>
       <x:c r="B4" s="4" t="str">
-        <x:v>本周飞书原值未取得，统一标记待核；不得用累计人数、办卡数或其他字段推算。</x:v>
+        <x:v>新客数取飞书门店数据汇总-周原值；老客数取飞书账单流水，按门店+会员ID在本周内去重。品牌新客1,150人、老客2,149人。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -507,38 +507,46 @@
         <x:v>续费率</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>门店续费率使用最新小程序截图原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
+        <x:v>门店续费率使用最新小程序截图中的“续卡率”原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="4" t="str">
-        <x:v>卡型率</x:v>
+        <x:v>引流/扫楼</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
+        <x:v>总引流金额和扫楼金额使用用户最终确认截图原值。品牌总引流173,051.70元，扫楼68,444.80元。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>总办卡率</x:v>
+        <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
+        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
-        <x:v>排名</x:v>
+        <x:v>总办卡率</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>店员卡型页保留截图排名；金额排名本周截图横向字段不完整，未用旧周数据冒充本周金额。</x:v>
+        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="4" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B9" s="4" t="str">
+        <x:v>店员卡型页保留截图排名；店长排名按已确认名单匹配本周金额截图，共21名店长。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="4" t="str">
         <x:v>更新方式</x:v>
       </x:c>
-      <x:c r="B9" s="4" t="str">
+      <x:c r="B10" s="4" t="str">
         <x:v>HTML、周报核对底表、城市经理问题闭环填写表使用同一周期和同一门店口径。</x:v>
       </x:c>
     </x:row>
@@ -985,7 +993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4a4fd26c8f845dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfc05ee1dba84503"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1155,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcda9e7b08e7a450f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f838dbb8d004d4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1346,7 +1354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R313c4d4c9e5f4943"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83f1b953db6e43ea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1516,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda614b0817134fd0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85eeec4c42f14404"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R36504bba54f045d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R86bf612cd5524223"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R64e1eb017a224a17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R6df2bdcbf32543b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R4b67c7f4166b4db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R91a1093d85124a16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R521dcda8aad649cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R6465ad83374d4815"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rf99f1d53ef5449af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R96a4730f7d244cf2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -993,7 +993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfc05ee1dba84503"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1408e61629aa4bce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1163,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f838dbb8d004d4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61625cc50144414b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1354,7 +1354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83f1b953db6e43ea"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34ebf95c7c94c76"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1524,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R85eeec4c42f14404"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42d778c569f94455"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R91a1093d85124a16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R521dcda8aad649cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R6465ad83374d4815"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rf99f1d53ef5449af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R96a4730f7d244cf2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R05cb51634de04a90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R62c3f1cdd00842dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R8360bd99ebcb4f86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Re36dd071c8434fba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rddb882e21a564f8e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable5" displayName="WeeklyTable5" ref="A1:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="WeeklyTable6" displayName="WeeklyTable6" ref="A1:G20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G20"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -224,7 +224,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable6" displayName="WeeklyTable6" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="WeeklyTable7" displayName="WeeklyTable7" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G7"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -240,7 +240,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WeeklyTable7" displayName="WeeklyTable7" ref="A1:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="WeeklyTable8" displayName="WeeklyTable8" ref="A1:G8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G8"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -256,7 +256,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable8" displayName="WeeklyTable8" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="WeeklyTable9" displayName="WeeklyTable9" ref="A1:G7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G7"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="状态"/>
@@ -993,7 +993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1408e61629aa4bce"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3937bd26ae254fc4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1163,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61625cc50144414b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4396cf06a1e94e22"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1354,7 +1354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd34ebf95c7c94c76"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda639227d8284744"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1524,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42d778c569f94455"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6bbc53c64248d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R05cb51634de04a90"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="R62c3f1cdd00842dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R8360bd99ebcb4f86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Re36dd071c8434fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rddb882e21a564f8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R87348ef530144b1d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rcae57e44b24340e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R1caf5364557548a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Re70caf2031344383"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R7a8acbc400dd4da6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -897,7 +897,7 @@
       </x:c>
       <x:c r="D16" s="18" t="str"/>
       <x:c r="E16" s="11" t="str">
-        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额1500；扫楼金额7715</x:v>
+        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额3600；扫楼金额7715</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
         <x:v>1. 总营收从33802元变为30206元，减少3596元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -956,15 +956,15 @@
         <x:v>安阳万达</x:v>
       </x:c>
       <x:c r="C19" s="17" t="str">
-        <x:v>完成率40.63%&lt;100%</x:v>
+        <x:v>完成率41.00%&lt;100%</x:v>
       </x:c>
       <x:c r="D19" s="18" t="str"/>
       <x:c r="E19" s="11" t="str">
-        <x:v>总营收7175；完成率40.63%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
+        <x:v>总营收7175；完成率41.00%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
         <x:v>1. 总营收从8389元变为7175元，减少1214元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
-2. 完成率40.63%，距目标还差10485元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
+2. 完成率41.00%，距目标还差10485元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡4张、中卡9张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G19" s="18" t="str"/>
@@ -993,7 +993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3937bd26ae254fc4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f8473d3d195427e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1163,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4396cf06a1e94e22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcfd6e069f9341ed"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1354,7 +1354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda639227d8284744"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a57e00b5d14eae"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1428,7 +1428,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额1500；扫楼金额7715</x:v>
+        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额3600；扫楼金额7715</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从33802元变为30206元，减少3596元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1487,15 +1487,15 @@
         <x:v>安阳万达</x:v>
       </x:c>
       <x:c r="C6" s="17" t="str">
-        <x:v>完成率40.63%&lt;100%</x:v>
+        <x:v>完成率41.00%&lt;100%</x:v>
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收7175；完成率40.63%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
+        <x:v>总营收7175；完成率41.00%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从8389元变为7175元，减少1214元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
-2. 完成率40.63%，距目标还差10485元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
+2. 完成率41.00%，距目标还差10485元。下周准备用新客量、客单价还是续卡拉齐？请给责任人、每日动作量和预计补回金额。
 3. 当前截图已识别新签小卡4张、中卡9张、大卡0张。请抽查最近5笔小卡成交：客户为什么没升卡、谁接待、卡在哪句话或报价顺序？</x:v>
       </x:c>
       <x:c r="G6" s="18" t="str"/>
@@ -1524,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb6bbc53c64248d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6fb6fcc40194eca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R87348ef530144b1d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rcae57e44b24340e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R1caf5364557548a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Re70caf2031344383"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R7a8acbc400dd4da6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rb5659d1339574335"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rdbedd4d3504d4030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R72586cc2df254c59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rb9f420c29d194939"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rffe625212e96478c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -993,7 +993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f8473d3d195427e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe2e971cb1e4f0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1163,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcfd6e069f9341ed"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60fc62cd047648e4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1354,7 +1354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79a57e00b5d14eae"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raae6be3f2f024ab7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1524,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6fb6fcc40194eca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f32b0e27d5f40e7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rb5659d1339574335"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rdbedd4d3504d4030"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R72586cc2df254c59"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="Rb9f420c29d194939"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="Rffe625212e96478c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R436ac470e618472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Re99f8b04e5184f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R6094aa59120e478e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R0c7d754d5ca944cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R780dd43529464d50"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -993,7 +993,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rffe2e971cb1e4f0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde126707eb0d429a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1163,7 +1163,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R60fc62cd047648e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f02ef3bb5db4d8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1354,7 +1354,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raae6be3f2f024ab7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7591fd4a5a854fc7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1524,7 +1524,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f32b0e27d5f40e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba158b24a8844c5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
+++ b/reports/current/城市经理问题闭环填写表_20260720-20260726.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="R436ac470e618472a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Re99f8b04e5184f6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R6094aa59120e478e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R0c7d754d5ca944cb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R780dd43529464d50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="口径说明" sheetId="1" r:id="Rdeb023d94ee24dc0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部区域" sheetId="2" r:id="Rf00ffae807e84f24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1区" sheetId="3" r:id="R7080d402d2dc418c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2区" sheetId="4" r:id="R79cef25e213e4b10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3区" sheetId="5" r:id="R548470b448b44138"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -504,49 +504,57 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="4" t="str">
-        <x:v>续费率</x:v>
+        <x:v>新签营收</x:v>
       </x:c>
       <x:c r="B5" s="4" t="str">
-        <x:v>门店续费率使用最新小程序截图中的“续卡率”原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
+        <x:v>新签营收=总营收-总续卡金额；小程序截图“新卡金额”只作为办卡模块原始值留档，不能替代新签营收。</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="4" t="str">
-        <x:v>引流/扫楼</x:v>
+        <x:v>续费率</x:v>
       </x:c>
       <x:c r="B6" s="4" t="str">
-        <x:v>总引流金额和扫楼金额使用用户最终确认截图原值。品牌总引流173,051.70元，扫楼68,444.80元。</x:v>
+        <x:v>门店续费率使用最新小程序截图中的“续卡率”原值，不自行反算；品牌续费率使用品牌截图原值8.10%。</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="4" t="str">
-        <x:v>卡型率</x:v>
+        <x:v>引流/扫楼</x:v>
       </x:c>
       <x:c r="B7" s="4" t="str">
-        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
+        <x:v>总引流金额和扫楼金额使用用户最终确认截图原值。品牌总引流173,051.70元，扫楼68,444.80元。</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="4" t="str">
-        <x:v>总办卡率</x:v>
+        <x:v>卡型率</x:v>
       </x:c>
       <x:c r="B8" s="4" t="str">
-        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
+        <x:v>新签小/中/大卡率=对应卡数/新签卡数；正式19店新签卡629张，卡型328/237/64。</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="4" t="str">
-        <x:v>排名</x:v>
+        <x:v>总办卡率</x:v>
       </x:c>
       <x:c r="B9" s="4" t="str">
-        <x:v>店员卡型页保留截图排名；店长排名按已确认名单匹配本周金额截图，共21名店长。</x:v>
+        <x:v>截图中的总办卡率与新签办卡率是两个不同指标，分别保留。</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="4" t="str">
+        <x:v>排名</x:v>
+      </x:c>
+      <x:c r="B10" s="4" t="str">
+        <x:v>店员卡型页保留截图排名；店长排名按已确认名单匹配本周金额截图，共21名店长。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="4" t="str">
         <x:v>更新方式</x:v>
       </x:c>
-      <x:c r="B10" s="4" t="str">
+      <x:c r="B11" s="4" t="str">
         <x:v>HTML、周报核对底表、城市经理问题闭环填写表使用同一周期和同一门店口径。</x:v>
       </x:c>
     </x:row>
@@ -603,7 +611,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收27207；完成率77.70%；新签营收21837；新签小/中/大卡43/20/2；续费率6.48%；续卡金额2768；扫楼金额3923</x:v>
+        <x:v>总营收27207；完成率77.70%；新签营收24439；新签小/中/大卡43/20/2；续费率6.48%；续卡金额2768；扫楼金额3923</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -624,7 +632,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收19374；完成率53.96%；新签营收11529；新签小/中/大卡22/8/2；续费率7.95%；续卡金额5949；扫楼金额2031</x:v>
+        <x:v>总营收19374；完成率53.96%；新签营收13425；新签小/中/大卡22/8/2；续费率7.95%；续卡金额5949；扫楼金额2031</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从21993元变为19374元，减少2619元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -645,7 +653,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收17482；完成率72.05%；新签营收9243；新签小/中/大卡15/11/0；续费率10%；续卡金额6280；扫楼金额3198</x:v>
+        <x:v>总营收17482；完成率72.05%；新签营收11202；新签小/中/大卡15/11/0；续费率10%；续卡金额6280；扫楼金额3198</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 本周总营收17482元，请列出贡献最大的3笔订单、员工和卡型。
@@ -666,7 +674,7 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收17406；完成率82.39%；新签营收7748；新签小/中/大卡14/5/5；续费率13.87%；续卡金额7964；扫楼金额2987</x:v>
+        <x:v>总营收17406；完成率82.39%；新签营收9442；新签小/中/大卡14/5/5；续费率13.87%；续卡金额7964；扫楼金额2987</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从15461元变为17406元，增加1945元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -687,7 +695,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收14716；完成率49.01%；新签营收9833；新签小/中/大卡18/6/3；续费率4.27%；续卡金额3399；扫楼金额491</x:v>
+        <x:v>总营收14716；完成率49.01%；新签营收11317；新签小/中/大卡18/6/3；续费率4.27%；续卡金额3399；扫楼金额491</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从24886元变为14716元，减少10170元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -708,7 +716,7 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收11921；完成率66.01%；新签营收9035；新签小/中/大卡8/18/1；续费率8%；续卡金额1486.15；扫楼金额3279.4</x:v>
+        <x:v>总营收11921；完成率66.01%；新签营收10435；新签小/中/大卡8/18/1；续费率8%；续卡金额1486.15；扫楼金额3279.4</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从10690元变为11921元，增加1231元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -729,7 +737,7 @@
       </x:c>
       <x:c r="D8" s="18" t="str"/>
       <x:c r="E8" s="11" t="str">
-        <x:v>总营收34016；完成率77.40%；新签营收16461；新签小/中/大卡22/11/6；续费率12.56%；续卡金额12299；扫楼金额8325</x:v>
+        <x:v>总营收34016；完成率77.40%；新签营收21717；新签小/中/大卡22/11/6；续费率12.56%；续卡金额12299；扫楼金额8325</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
         <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -750,7 +758,7 @@
       </x:c>
       <x:c r="D9" s="18" t="str"/>
       <x:c r="E9" s="11" t="str">
-        <x:v>总营收18990；完成率76.64%；新签营收14184；新签小/中/大卡35/12/0；续费率4.3%；续卡金额1600；扫楼金额3349</x:v>
+        <x:v>总营收18990；完成率76.64%；新签营收17390；新签小/中/大卡35/12/0；续费率4.3%；续卡金额1600；扫楼金额3349</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
         <x:v>1. 总营收从15679元变为18990元，增加3311元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -771,7 +779,7 @@
       </x:c>
       <x:c r="D10" s="18" t="str"/>
       <x:c r="E10" s="11" t="str">
-        <x:v>总营收12223；完成率56.45%；新签营收8912；新签小/中/大卡4/13/1；续费率7.87%；续卡金额3200；扫楼金额2782</x:v>
+        <x:v>总营收12223；完成率56.45%；新签营收9023；新签小/中/大卡4/13/1；续费率7.87%；续卡金额3200；扫楼金额2782</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
         <x:v>1. 总营收从17422元变为12223元，减少5199元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -792,7 +800,7 @@
       </x:c>
       <x:c r="D11" s="18" t="str"/>
       <x:c r="E11" s="11" t="str">
-        <x:v>总营收11731；完成率61.88%；新签营收4837；新签小/中/大卡4/8/0；续费率5.26%；续卡金额2800；扫楼金额2243.2</x:v>
+        <x:v>总营收11731；完成率61.88%；新签营收8931；新签小/中/大卡4/8/0；续费率5.26%；续卡金额2800；扫楼金额2243.2</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
         <x:v>1. 总营收从14444元变为11731元，减少2713元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -813,7 +821,7 @@
       </x:c>
       <x:c r="D12" s="18" t="str"/>
       <x:c r="E12" s="11" t="str">
-        <x:v>总营收36882；完成率91.25%；新签营收15240；新签小/中/大卡23/19/0；续费率7.34%；续卡金额17800；扫楼金额8531.2</x:v>
+        <x:v>总营收36882；完成率91.25%；新签营收19082；新签小/中/大卡23/19/0；续费率7.34%；续卡金额17800；扫楼金额8531.2</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
         <x:v>1. 总营收从32869元变为36882元，增加4014元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -834,7 +842,7 @@
       </x:c>
       <x:c r="D13" s="18" t="str"/>
       <x:c r="E13" s="11" t="str">
-        <x:v>总营收16093；完成率84.85%；新签营收11008；新签小/中/大卡1/10/16；续费率13.75%；续卡金额4089；扫楼金额3069</x:v>
+        <x:v>总营收16093；完成率84.85%；新签营收12004；新签小/中/大卡1/10/16；续费率13.75%；续卡金额4089；扫楼金额3069</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
         <x:v>1. 总营收从13881元变为16093元，增加2212元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -855,7 +863,7 @@
       </x:c>
       <x:c r="D14" s="18" t="str"/>
       <x:c r="E14" s="11" t="str">
-        <x:v>总营收27184；完成率133.32%；新签营收22423；新签小/中/大卡9/21/5；续费率5.1%；续卡金额1800；扫楼金额1814</x:v>
+        <x:v>总营收27184；完成率133.32%；新签营收25384；新签小/中/大卡9/21/5；续费率5.1%；续卡金额1800；扫楼金额1814</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
         <x:v>1. 总营收从14630元变为27184元，增加12553元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -876,7 +884,7 @@
       </x:c>
       <x:c r="D15" s="18" t="str"/>
       <x:c r="E15" s="11" t="str">
-        <x:v>总营收30549；完成率89.02%；新签营收20415；新签小/中/大卡32/17/2；续费率11.11%；续卡金额6900；扫楼金额9649</x:v>
+        <x:v>总营收30549；完成率89.02%；新签营收23649；新签小/中/大卡32/17/2；续费率11.11%；续卡金额6900；扫楼金额9649</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
         <x:v>1. 总营收从24097元变为30549元，增加6452元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -897,7 +905,7 @@
       </x:c>
       <x:c r="D16" s="18" t="str"/>
       <x:c r="E16" s="11" t="str">
-        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额3600；扫楼金额7715</x:v>
+        <x:v>总营收30206；完成率68.71%；新签营收26606；新签小/中/大卡37/14/6；续费率4.55%；续卡金额3600；扫楼金额7715</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
         <x:v>1. 总营收从33802元变为30206元，减少3596元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -918,7 +926,7 @@
       </x:c>
       <x:c r="D17" s="18" t="str"/>
       <x:c r="E17" s="11" t="str">
-        <x:v>总营收21882；完成率70.36%；新签营收11554；新签小/中/大卡16/9/3；续费率8.93%；续卡金额7400；扫楼金额2287</x:v>
+        <x:v>总营收21882；完成率70.36%；新签营收14482；新签小/中/大卡16/9/3；续费率8.93%；续卡金额7400；扫楼金额2287</x:v>
       </x:c>
       <x:c r="F17" s="11" t="str">
         <x:v>1. 总营收从20896元变为21882元，增加986元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -939,7 +947,7 @@
       </x:c>
       <x:c r="D18" s="18" t="str"/>
       <x:c r="E18" s="11" t="str">
-        <x:v>总营收8696；完成率52.35%；新签营收5862；新签小/中/大卡3/6/8；续费率7.32%；续卡金额957；扫楼金额1771</x:v>
+        <x:v>总营收8696；完成率52.35%；新签营收7739；新签小/中/大卡3/6/8；续费率7.32%；续卡金额957；扫楼金额1771</x:v>
       </x:c>
       <x:c r="F18" s="11" t="str">
         <x:v>1. 本周总营收8696元，请列出贡献最大的3笔订单、员工和卡型。
@@ -960,7 +968,7 @@
       </x:c>
       <x:c r="D19" s="18" t="str"/>
       <x:c r="E19" s="11" t="str">
-        <x:v>总营收7175；完成率41.00%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
+        <x:v>总营收7175；完成率41.00%；新签营收7175；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
       </x:c>
       <x:c r="F19" s="11" t="str">
         <x:v>1. 总营收从8389元变为7175元，减少1214元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -981,7 +989,7 @@
       </x:c>
       <x:c r="D20" s="18" t="str"/>
       <x:c r="E20" s="11" t="str">
-        <x:v>总营收25527；完成率78.67%；新签营收17570；新签小/中/大卡18/20/4；续费率7.83%；续卡金额3920；扫楼金额1000</x:v>
+        <x:v>总营收25527；完成率78.67%；新签营收21607；新签小/中/大卡18/20/4；续费率7.83%；续卡金额3920；扫楼金额1000</x:v>
       </x:c>
       <x:c r="F20" s="11" t="str">
         <x:v>1. 总营收从29658元变为25527元，减少4131元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -993,7 +1001,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde126707eb0d429a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25acbc3cf54d4e69"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1046,7 +1054,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收27207；完成率77.70%；新签营收21837；新签小/中/大卡43/20/2；续费率6.48%；续卡金额2768；扫楼金额3923</x:v>
+        <x:v>总营收27207；完成率77.70%；新签营收24439；新签小/中/大卡43/20/2；续费率6.48%；续卡金额2768；扫楼金额3923</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从26293元变为27207元，增加915元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1067,7 +1075,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收19374；完成率53.96%；新签营收11529；新签小/中/大卡22/8/2；续费率7.95%；续卡金额5949；扫楼金额2031</x:v>
+        <x:v>总营收19374；完成率53.96%；新签营收13425；新签小/中/大卡22/8/2；续费率7.95%；续卡金额5949；扫楼金额2031</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从21993元变为19374元，减少2619元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1088,7 +1096,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收17482；完成率72.05%；新签营收9243；新签小/中/大卡15/11/0；续费率10%；续卡金额6280；扫楼金额3198</x:v>
+        <x:v>总营收17482；完成率72.05%；新签营收11202；新签小/中/大卡15/11/0；续费率10%；续卡金额6280；扫楼金额3198</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 本周总营收17482元，请列出贡献最大的3笔订单、员工和卡型。
@@ -1109,7 +1117,7 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收17406；完成率82.39%；新签营收7748；新签小/中/大卡14/5/5；续费率13.87%；续卡金额7964；扫楼金额2987</x:v>
+        <x:v>总营收17406；完成率82.39%；新签营收9442；新签小/中/大卡14/5/5；续费率13.87%；续卡金额7964；扫楼金额2987</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从15461元变为17406元，增加1945元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1130,7 +1138,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收14716；完成率49.01%；新签营收9833；新签小/中/大卡18/6/3；续费率4.27%；续卡金额3399；扫楼金额491</x:v>
+        <x:v>总营收14716；完成率49.01%；新签营收11317；新签小/中/大卡18/6/3；续费率4.27%；续卡金额3399；扫楼金额491</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从24886元变为14716元，减少10170元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1151,7 +1159,7 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收11921；完成率66.01%；新签营收9035；新签小/中/大卡8/18/1；续费率8%；续卡金额1486.15；扫楼金额3279.4</x:v>
+        <x:v>总营收11921；完成率66.01%；新签营收10435；新签小/中/大卡8/18/1；续费率8%；续卡金额1486.15；扫楼金额3279.4</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从10690元变为11921元，增加1231元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1163,7 +1171,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f02ef3bb5db4d8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a6a5452cebb409a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1216,7 +1224,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收34016；完成率77.40%；新签营收16461；新签小/中/大卡22/11/6；续费率12.56%；续卡金额12299；扫楼金额8325</x:v>
+        <x:v>总营收34016；完成率77.40%；新签营收21717；新签小/中/大卡22/11/6；续费率12.56%；续卡金额12299；扫楼金额8325</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从65202元变为34016元，减少31186元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1237,7 +1245,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收18990；完成率76.64%；新签营收14184；新签小/中/大卡35/12/0；续费率4.3%；续卡金额1600；扫楼金额3349</x:v>
+        <x:v>总营收18990；完成率76.64%；新签营收17390；新签小/中/大卡35/12/0；续费率4.3%；续卡金额1600；扫楼金额3349</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从15679元变为18990元，增加3311元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1258,7 +1266,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收12223；完成率56.45%；新签营收8912；新签小/中/大卡4/13/1；续费率7.87%；续卡金额3200；扫楼金额2782</x:v>
+        <x:v>总营收12223；完成率56.45%；新签营收9023；新签小/中/大卡4/13/1；续费率7.87%；续卡金额3200；扫楼金额2782</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 总营收从17422元变为12223元，减少5199元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1279,7 +1287,7 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收11731；完成率61.88%；新签营收4837；新签小/中/大卡4/8/0；续费率5.26%；续卡金额2800；扫楼金额2243.2</x:v>
+        <x:v>总营收11731；完成率61.88%；新签营收8931；新签小/中/大卡4/8/0；续费率5.26%；续卡金额2800；扫楼金额2243.2</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 总营收从14444元变为11731元，减少2713元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1300,7 +1308,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收36882；完成率91.25%；新签营收15240；新签小/中/大卡23/19/0；续费率7.34%；续卡金额17800；扫楼金额8531.2</x:v>
+        <x:v>总营收36882；完成率91.25%；新签营收19082；新签小/中/大卡23/19/0；续费率7.34%；续卡金额17800；扫楼金额8531.2</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从32869元变为36882元，增加4014元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1321,7 +1329,7 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收16093；完成率84.85%；新签营收11008；新签小/中/大卡1/10/16；续费率13.75%；续卡金额4089；扫楼金额3069</x:v>
+        <x:v>总营收16093；完成率84.85%；新签营收12004；新签小/中/大卡1/10/16；续费率13.75%；续卡金额4089；扫楼金额3069</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从13881元变为16093元，增加2212元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1342,7 +1350,7 @@
       </x:c>
       <x:c r="D8" s="18" t="str"/>
       <x:c r="E8" s="11" t="str">
-        <x:v>总营收27184；完成率133.32%；新签营收22423；新签小/中/大卡9/21/5；续费率5.1%；续卡金额1800；扫楼金额1814</x:v>
+        <x:v>总营收27184；完成率133.32%；新签营收25384；新签小/中/大卡9/21/5；续费率5.1%；续卡金额1800；扫楼金额1814</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
         <x:v>1. 总营收从14630元变为27184元，增加12553元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1354,7 +1362,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7591fd4a5a854fc7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ad60e4a6dcf4df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1407,7 +1415,7 @@
       </x:c>
       <x:c r="D2" s="18" t="str"/>
       <x:c r="E2" s="11" t="str">
-        <x:v>总营收30549；完成率89.02%；新签营收20415；新签小/中/大卡32/17/2；续费率11.11%；续卡金额6900；扫楼金额9649</x:v>
+        <x:v>总营收30549；完成率89.02%；新签营收23649；新签小/中/大卡32/17/2；续费率11.11%；续卡金额6900；扫楼金额9649</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>1. 总营收从24097元变为30549元，增加6452元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1428,7 +1436,7 @@
       </x:c>
       <x:c r="D3" s="18" t="str"/>
       <x:c r="E3" s="11" t="str">
-        <x:v>总营收30206；完成率68.71%；新签营收24256；新签小/中/大卡37/14/6；续费率4.55%；续卡金额3600；扫楼金额7715</x:v>
+        <x:v>总营收30206；完成率68.71%；新签营收26606；新签小/中/大卡37/14/6；续费率4.55%；续卡金额3600；扫楼金额7715</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>1. 总营收从33802元变为30206元，减少3596元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1449,7 +1457,7 @@
       </x:c>
       <x:c r="D4" s="18" t="str"/>
       <x:c r="E4" s="11" t="str">
-        <x:v>总营收21882；完成率70.36%；新签营收11554；新签小/中/大卡16/9/3；续费率8.93%；续卡金额7400；扫楼金额2287</x:v>
+        <x:v>总营收21882；完成率70.36%；新签营收14482；新签小/中/大卡16/9/3；续费率8.93%；续卡金额7400；扫楼金额2287</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
         <x:v>1. 总营收从20896元变为21882元，增加986元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1470,7 +1478,7 @@
       </x:c>
       <x:c r="D5" s="18" t="str"/>
       <x:c r="E5" s="11" t="str">
-        <x:v>总营收8696；完成率52.35%；新签营收5862；新签小/中/大卡3/6/8；续费率7.32%；续卡金额957；扫楼金额1771</x:v>
+        <x:v>总营收8696；完成率52.35%；新签营收7739；新签小/中/大卡3/6/8；续费率7.32%；续卡金额957；扫楼金额1771</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
         <x:v>1. 本周总营收8696元，请列出贡献最大的3笔订单、员工和卡型。
@@ -1491,7 +1499,7 @@
       </x:c>
       <x:c r="D6" s="18" t="str"/>
       <x:c r="E6" s="11" t="str">
-        <x:v>总营收7175；完成率41.00%；新签营收5599；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
+        <x:v>总营收7175；完成率41.00%；新签营收7175；新签小/中/大卡4/9/0；续费率0%；续卡金额0；扫楼金额0</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
         <x:v>1. 总营收从8389元变为7175元，减少1214元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1512,7 +1520,7 @@
       </x:c>
       <x:c r="D7" s="18" t="str"/>
       <x:c r="E7" s="11" t="str">
-        <x:v>总营收25527；完成率78.67%；新签营收17570；新签小/中/大卡18/20/4；续费率7.83%；续卡金额3920；扫楼金额1000</x:v>
+        <x:v>总营收25527；完成率78.67%；新签营收21607；新签小/中/大卡18/20/4；续费率7.83%；续卡金额3920；扫楼金额1000</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
         <x:v>1. 总营收从29658元变为25527元，减少4131元。请拆出影响最大的3笔订单、员工和卡型；剔除这3笔后真实趋势是什么？
@@ -1524,7 +1532,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba158b24a8844c5a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2814975754804048"/>
   </x:tableParts>
 </x:worksheet>
 </file>